--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>62.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-24.0</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,11 @@
           <t>diff_fora</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-28.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (9)</t>
+          <t>Q1 (3)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-18)</t>
+          <t>Q2 (-16.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,12 +701,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (9)</t>
+          <t>Diff médio casa: -20 | fora: -28</t>
         </is>
       </c>
     </row>
@@ -714,12 +718,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pior período: Q2 (-18)</t>
+          <t>Melhor período: Q1 (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pior período: Q2 (-16.5)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -794,38 +810,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="n">
+        <v>88</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>84</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F3" t="n">
         <v>-20</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>64</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H3" t="n">
         <v>84</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I3" t="n">
         <v>-20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,202 +973,250 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.6</v>
+        <v>30.5</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>-22</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+        <v>-23</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.9</v>
+        <v>38.6</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+        <v>-22</v>
+      </c>
+      <c r="E3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-30</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>-26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.5</v>
+        <v>24.2</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>-24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-9</v>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-16.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>39.9</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-23</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="K5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-20.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
       <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31.6</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>-25</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-7</v>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.8</v>
+        <v>31.6</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>-25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-21</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>-23</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-4</v>
+      </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>27</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-23</v>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>-23</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -1127,28 +1224,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. Sousa</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>O. Onyeka</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-28</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-1</v>
+        <v>-28</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1260,25 +1357,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1400,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>-18</v>
+        <v>-33</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-18</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1443,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="G4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1486,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-14</v>
+        <v>-9.5</v>
       </c>
     </row>
   </sheetData>
@@ -1422,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1538,22 +1635,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -1565,16 +1662,16 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -1583,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1593,62 +1690,62 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1657,37 +1754,37 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1699,67 +1796,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -1768,124 +1873,203 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. Neto</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
       <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>J. Bertino</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>M. Pombo</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="B9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q8"/>
+  <autoFilter ref="A1:Q9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1896,11 +2080,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -1974,8 +2158,37 @@
         <v>-20</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922725</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Portugal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" t="n">
+        <v>88</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>68.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-24.0</t>
+          <t>-20.0</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-12.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (3)</t>
+          <t>Q1 (2.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-16.5)</t>
+          <t>Q2 (-12.7)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: -20 | fora: -28</t>
+          <t>Diff médio casa: -12 | fora: -28</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (3)</t>
+          <t>Melhor período: Q1 (2.7)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q2 (-16.5)</t>
+          <t>Pior período: Q2 (-12.7)</t>
         </is>
       </c>
     </row>
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="F3" t="n">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="G3" t="n">
-        <v>64</v>
+        <v>77.5</v>
       </c>
       <c r="H3" t="n">
-        <v>84</v>
+        <v>89.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-20</v>
+        <v>-12</v>
       </c>
     </row>
   </sheetData>
@@ -973,108 +973,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>J. Bailey</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.5</v>
+        <v>38.9</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>-23</v>
+        <v>-13.5</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>34.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>-30</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. Bailey</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.6</v>
+        <v>35.8</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>-22</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>34.8</v>
+        <v>33.1</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-26</v>
+        <v>-13</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. Bertino</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.2</v>
+        <v>19.9</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-24</v>
+        <v>-13.5</v>
       </c>
       <c r="E4" t="n">
-        <v>16.2</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>-16.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.9</v>
+        <v>39.2</v>
       </c>
       <c r="C5" t="n">
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="E5" t="n">
         <v>33.5</v>
@@ -1108,10 +1108,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>15.5</v>
+        <v>16.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.5</v>
+        <v>-13</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
@@ -1121,133 +1121,149 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>J. Bertino</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>-14</v>
       </c>
       <c r="E6" t="n">
-        <v>11.5</v>
+        <v>16.2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
+        <v>-12.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.6</v>
+        <v>15.9</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>-25</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="n">
-        <v>25.9</v>
+        <v>11.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>-23</v>
+        <v>-3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. Carr</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>F. Ferreira</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-12</v>
+      </c>
       <c r="E8" t="n">
-        <v>35.7</v>
+        <v>25.9</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>-23</v>
+        <v>-21</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1</v>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>D. Carr</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
       <c r="E9" t="n">
-        <v>33.1</v>
+        <v>35.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>-28</v>
+        <v>-23</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>-10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-3</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1357,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>20.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -1400,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H3" t="n">
-        <v>-33</v>
+        <v>-38</v>
       </c>
       <c r="I3" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="J3" t="n">
         <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-16.5</v>
+        <v>-12.7</v>
       </c>
     </row>
     <row r="4">
@@ -1443,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I4" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>20.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="5">
@@ -1486,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>-19</v>
+        <v>-12</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.5</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -1638,49 +1654,49 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1690,52 +1706,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="4">
@@ -1748,40 +1764,40 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1796,111 +1812,111 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
         <v>1.5</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="Q5" t="n">
         <v>0.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -1913,26 +1929,26 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
@@ -1952,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1965,7 +1981,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1974,16 +1990,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1998,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2020,7 +2036,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -2032,16 +2048,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2050,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2080,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2187,8 +2203,37 @@
         <v>-28</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922731</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>91</v>
+      </c>
+      <c r="F4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_ESG.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>73.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>92.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-20.0</t>
+          <t>-19.0</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-28.0</t>
+          <t>-26.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q1 (2.7)</t>
+          <t>Q1 (2.2)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-12.7)</t>
+          <t>Q2 (-15.5)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: -12 | fora: -28</t>
+          <t>Diff médio casa: -12 | fora: -26</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Melhor período: Q1 (2.7)</t>
+          <t>Melhor período: Q1 (2.2)</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pior período: Q2 (-12.7)</t>
+          <t>Pior período: Q2 (-15.5)</t>
         </is>
       </c>
     </row>
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="F2" t="n">
-        <v>-28</v>
+        <v>-52</v>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>-28</v>
+        <v>-26</v>
       </c>
     </row>
     <row r="3">
@@ -986,132 +986,132 @@
         <v>-13.5</v>
       </c>
       <c r="E2" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>-30</v>
+        <v>-25.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-19</v>
+        <v>-19.5</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. Onyeka</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.8</v>
+        <v>39.2</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="E3" t="n">
-        <v>33.1</v>
+        <v>30.4</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-28</v>
+        <v>-21.5</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>10.5</v>
+        <v>12.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-13</v>
+        <v>-14.8</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. Antonio</t>
+          <t>O. Onyeka</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.9</v>
+        <v>35.8</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>-13.5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>28.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>10.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>Y. Antonio</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39.2</v>
+        <v>19.9</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-8</v>
+        <v>-13.5</v>
       </c>
       <c r="E5" t="n">
-        <v>33.5</v>
+        <v>11.1</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-23</v>
+        <v>-6.5</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>16.3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
@@ -1134,21 +1134,21 @@
         <v>-14</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2</v>
+        <v>11.1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-9</v>
+        <v>-7.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-12.3</v>
+        <v>-10.8</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -1158,34 +1158,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. Pombo</t>
+          <t>F. Ferreira</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.9</v>
+        <v>27.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="E7" t="n">
-        <v>11.5</v>
+        <v>22.6</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-7</v>
+        <v>-14.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>7.8</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.7</v>
+        <v>-13.2</v>
       </c>
       <c r="L7" t="n">
         <v>0.5</v>
@@ -1195,37 +1195,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. Ferreira</t>
+          <t>M. Pombo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.8</v>
+        <v>15.9</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="D8" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="n">
-        <v>25.9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-21</v>
+        <v>-5</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>8.300000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="n">
-        <v>-15</v>
+        <v>-3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -1245,24 +1245,24 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>35.7</v>
+        <v>34.9</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>-23</v>
+        <v>-26.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="K9" t="n">
-        <v>-10</v>
+        <v>-16.7</v>
       </c>
       <c r="L9" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="J2" t="n">
-        <v>20.3</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="H3" t="n">
-        <v>-38</v>
+        <v>-62</v>
       </c>
       <c r="I3" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.7</v>
+        <v>-15.5</v>
       </c>
     </row>
     <row r="4">
@@ -1459,25 +1459,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="I4" t="n">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="5">
@@ -1502,25 +1502,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="H5" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-4</v>
+        <v>-2.2</v>
       </c>
     </row>
   </sheetData>
@@ -1651,49 +1651,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -1702,111 +1702,111 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. Carvalhal</t>
+          <t>D. Carr</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F3" t="n">
         <v>3.7</v>
       </c>
-      <c r="C3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.3</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0.7</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>1.3</v>
-      </c>
       <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Carr</t>
+          <t>P. Carvalhal</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="C4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L4" t="n">
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1816,52 +1816,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -1871,52 +1871,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1926,28 +1926,28 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F7" t="n">
         <v>0.7</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1993,13 +1993,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2051,10 +2051,10 @@
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I9" t="n">
         <v>0.3</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2232,8 +2232,37 @@
         <v>-4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922738</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="n">
+        <v>104</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>